--- a/docs/downloads/04/tbl_class_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_class_alaotra_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E118"/>
+  <dimension ref="A1:E116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -397,12 +397,6 @@
           <t>Primaire</t>
         </is>
       </c>
-      <c r="D2">
-        <v>4</v>
-      </c>
-      <c r="E2">
-        <v>66.7</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -420,12 +414,6 @@
           <t>Secondaire 1er cycle</t>
         </is>
       </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>33.3</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -443,12 +431,6 @@
           <t>Primaire</t>
         </is>
       </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>42.9</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -466,12 +448,6 @@
           <t>Secondaire 1er cycle</t>
         </is>
       </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>57.1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -532,14 +508,8 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>25</v>
+          <t>Primaire</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -555,14 +525,8 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9">
-        <v>50</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -578,14 +542,8 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>25</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -716,14 +674,8 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-      <c r="E16">
-        <v>12.5</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -785,14 +737,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E19">
-        <v>18.6</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="20">
@@ -803,19 +755,13 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>2</v>
-      </c>
-      <c r="E20">
-        <v>4.7</v>
+          <t>Primaire</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -831,14 +777,8 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>2</v>
-      </c>
-      <c r="E21">
-        <v>50</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -849,7 +789,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -858,10 +798,10 @@
         </is>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E22">
-        <v>50</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="23">
@@ -877,14 +817,8 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>5</v>
-      </c>
-      <c r="E23">
-        <v>15.6</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -900,37 +834,37 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D24">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E24">
-        <v>81.2</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6-10 ans</t>
+          <t>11-14 ans</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E25">
-        <v>3.1</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="26">
@@ -946,14 +880,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D26">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E26">
-        <v>52.9</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="27">
@@ -969,14 +903,8 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D27">
-        <v>7</v>
-      </c>
-      <c r="E27">
-        <v>41.2</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -987,19 +915,13 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11-14 ans</t>
+          <t>15-17 ans</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-      <c r="E28">
-        <v>5.9</v>
+          <t>Primaire</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -1015,14 +937,8 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>4</v>
-      </c>
-      <c r="E29">
-        <v>44.4</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1038,14 +954,8 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D30">
-        <v>3</v>
-      </c>
-      <c r="E30">
-        <v>33.3</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -1056,19 +966,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>15-17 ans</t>
+          <t>18-25 ans</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E31">
-        <v>22.2</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="32">
@@ -1084,14 +994,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D32">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E32">
-        <v>43.3</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="33">
@@ -1107,14 +1017,8 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D33">
-        <v>14</v>
-      </c>
-      <c r="E33">
-        <v>46.7</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -1125,19 +1029,13 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D34">
-        <v>3</v>
-      </c>
-      <c r="E34">
-        <v>10</v>
+          <t>Primaire</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -1153,14 +1051,8 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D35">
-        <v>3</v>
-      </c>
-      <c r="E35">
-        <v>75</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -1171,7 +1063,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1180,10 +1072,10 @@
         </is>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E36">
-        <v>25</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="37">
@@ -1199,25 +1091,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D37">
-        <v>2</v>
-      </c>
-      <c r="E37">
-        <v>8.300000000000001</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6-10 ans</t>
+          <t>11-14 ans</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1226,10 +1112,10 @@
         </is>
       </c>
       <c r="D38">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E38">
-        <v>91.7</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="39">
@@ -1245,14 +1131,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D39">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E39">
-        <v>64.7</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="40">
@@ -1263,19 +1149,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11-14 ans</t>
+          <t>15-17 ans</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E40">
-        <v>35.3</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41">
@@ -1291,14 +1177,8 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D41">
-        <v>7</v>
-      </c>
-      <c r="E41">
-        <v>70</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -1309,19 +1189,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15-17 ans</t>
+          <t>18-25 ans</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E42">
-        <v>30</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43">
@@ -1337,14 +1217,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D43">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E43">
-        <v>59</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="44">
@@ -1360,14 +1240,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D44">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E44">
-        <v>25.6</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="45">
@@ -1378,19 +1258,13 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D45">
-        <v>4</v>
-      </c>
-      <c r="E45">
-        <v>10.3</v>
+          <t>Primaire</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -1401,19 +1275,13 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D46">
-        <v>2</v>
-      </c>
-      <c r="E46">
-        <v>5.1</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -1424,19 +1292,19 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E47">
-        <v>50</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="48">
@@ -1447,19 +1315,13 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D48">
-        <v>1</v>
-      </c>
-      <c r="E48">
-        <v>50</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -1475,25 +1337,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D49">
-        <v>1</v>
-      </c>
-      <c r="E49">
-        <v>6.2</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>6-10 ans</t>
+          <t>11-14 ans</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1502,33 +1358,27 @@
         </is>
       </c>
       <c r="D50">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E50">
-        <v>87.5</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6-10 ans</t>
+          <t>11-14 ans</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
           <t>Secondaire 1er cycle</t>
         </is>
-      </c>
-      <c r="D51">
-        <v>1</v>
-      </c>
-      <c r="E51">
-        <v>6.2</v>
       </c>
     </row>
     <row r="52">
@@ -1539,7 +1389,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11-14 ans</t>
+          <t>15-17 ans</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1548,10 +1398,10 @@
         </is>
       </c>
       <c r="D52">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E52">
-        <v>76.5</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="53">
@@ -1562,19 +1412,13 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>11-14 ans</t>
+          <t>15-17 ans</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
           <t>Secondaire 1er cycle</t>
         </is>
-      </c>
-      <c r="D53">
-        <v>4</v>
-      </c>
-      <c r="E53">
-        <v>23.5</v>
       </c>
     </row>
     <row r="54">
@@ -1590,14 +1434,8 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D54">
-        <v>5</v>
-      </c>
-      <c r="E54">
-        <v>62.5</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -1608,19 +1446,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>15-17 ans</t>
+          <t>18-25 ans</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D55">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E55">
-        <v>25</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="56">
@@ -1631,19 +1469,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>15-17 ans</t>
+          <t>18-25 ans</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E56">
-        <v>12.5</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="57">
@@ -1659,14 +1497,8 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D57">
-        <v>8</v>
-      </c>
-      <c r="E57">
-        <v>36.4</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -1677,19 +1509,13 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D58">
-        <v>10</v>
-      </c>
-      <c r="E58">
-        <v>45.5</v>
+          <t>Primaire</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -1700,19 +1526,13 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D59">
-        <v>4</v>
-      </c>
-      <c r="E59">
-        <v>18.2</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -1723,19 +1543,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D60">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E60">
-        <v>66.7</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="61">
@@ -1746,19 +1566,13 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D61">
-        <v>2</v>
-      </c>
-      <c r="E61">
-        <v>33.3</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -1774,7 +1588,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D62">
@@ -1787,12 +1601,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>6-10 ans</t>
+          <t>11-14 ans</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1801,21 +1615,21 @@
         </is>
       </c>
       <c r="D63">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E63">
-        <v>69.2</v>
+        <v>63</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6-10 ans</t>
+          <t>11-14 ans</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1824,10 +1638,10 @@
         </is>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E64">
-        <v>3.8</v>
+        <v>37</v>
       </c>
     </row>
     <row r="65">
@@ -1838,7 +1652,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>11-14 ans</t>
+          <t>15-17 ans</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1847,10 +1661,10 @@
         </is>
       </c>
       <c r="D65">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E65">
-        <v>63</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="66">
@@ -1861,7 +1675,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>11-14 ans</t>
+          <t>15-17 ans</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1870,10 +1684,10 @@
         </is>
       </c>
       <c r="D66">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E66">
-        <v>37</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67">
@@ -1889,14 +1703,8 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D67">
-        <v>6</v>
-      </c>
-      <c r="E67">
-        <v>42.9</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -1907,19 +1715,19 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>15-17 ans</t>
+          <t>18-25 ans</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D68">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E68">
-        <v>50</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="69">
@@ -1930,19 +1738,19 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15-17 ans</t>
+          <t>18-25 ans</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E69">
-        <v>7.1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="70">
@@ -1958,14 +1766,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D70">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E70">
-        <v>59.1</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="71">
@@ -1976,19 +1784,19 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D71">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E71">
-        <v>25</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="72">
@@ -1999,19 +1807,13 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D72">
-        <v>7</v>
-      </c>
-      <c r="E72">
-        <v>15.9</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -2022,19 +1824,19 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D73">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="E73">
-        <v>28.6</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="74">
@@ -2045,65 +1847,53 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D74">
-        <v>5</v>
-      </c>
-      <c r="E74">
-        <v>71.40000000000001</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>6-10 ans</t>
+          <t>11-14 ans</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D75">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="E75">
-        <v>7.3</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>6-10 ans</t>
+          <t>11-14 ans</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D76">
-        <v>38</v>
-      </c>
-      <c r="E76">
-        <v>92.7</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -2114,7 +1904,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>11-14 ans</t>
+          <t>15-17 ans</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2123,10 +1913,10 @@
         </is>
       </c>
       <c r="D77">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E77">
-        <v>90.90000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="78">
@@ -2137,7 +1927,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>11-14 ans</t>
+          <t>15-17 ans</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2146,10 +1936,10 @@
         </is>
       </c>
       <c r="D78">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E78">
-        <v>9.1</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="79">
@@ -2165,14 +1955,8 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D79">
-        <v>9</v>
-      </c>
-      <c r="E79">
-        <v>60</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -2183,19 +1967,19 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>15-17 ans</t>
+          <t>18-25 ans</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D80">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="E80">
-        <v>33.3</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="81">
@@ -2206,19 +1990,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>15-17 ans</t>
+          <t>18-25 ans</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E81">
-        <v>6.7</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="82">
@@ -2234,14 +2018,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D82">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E82">
-        <v>44.4</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="83">
@@ -2252,19 +2036,13 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D83">
-        <v>14</v>
-      </c>
-      <c r="E83">
-        <v>25.9</v>
+          <t>Primaire</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -2275,19 +2053,19 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D84">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E84">
-        <v>27.8</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="85">
@@ -2298,19 +2076,19 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E85">
-        <v>1.9</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="86">
@@ -2321,30 +2099,24 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D86">
-        <v>7</v>
-      </c>
-      <c r="E86">
-        <v>77.8</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>11-14 ans</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2353,44 +2125,44 @@
         </is>
       </c>
       <c r="D87">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E87">
-        <v>22.2</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>6-10 ans</t>
+          <t>11-14 ans</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D88">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E88">
-        <v>7.7</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>6-10 ans</t>
+          <t>15-17 ans</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2399,10 +2171,10 @@
         </is>
       </c>
       <c r="D89">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E89">
-        <v>92.3</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="90">
@@ -2413,19 +2185,19 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>11-14 ans</t>
+          <t>15-17 ans</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D90">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E90">
-        <v>65.5</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="91">
@@ -2436,19 +2208,13 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>11-14 ans</t>
+          <t>15-17 ans</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D91">
-        <v>10</v>
-      </c>
-      <c r="E91">
-        <v>34.5</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -2459,7 +2225,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15-17 ans</t>
+          <t>18-25 ans</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2468,7 +2234,7 @@
         </is>
       </c>
       <c r="D92">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E92">
         <v>33.3</v>
@@ -2482,7 +2248,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>15-17 ans</t>
+          <t>18-25 ans</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2491,10 +2257,10 @@
         </is>
       </c>
       <c r="D93">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E93">
-        <v>55.6</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="94">
@@ -2505,19 +2271,19 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15-17 ans</t>
+          <t>18-25 ans</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D94">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E94">
-        <v>11.1</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="95">
@@ -2528,19 +2294,13 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
           <t>Primaire</t>
         </is>
-      </c>
-      <c r="D95">
-        <v>12</v>
-      </c>
-      <c r="E95">
-        <v>33.3</v>
       </c>
     </row>
     <row r="96">
@@ -2551,19 +2311,13 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D96">
-        <v>16</v>
-      </c>
-      <c r="E96">
-        <v>44.4</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -2574,19 +2328,13 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D97">
-        <v>8</v>
-      </c>
-      <c r="E97">
-        <v>22.2</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -2597,19 +2345,19 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="E98">
-        <v>33.3</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="99">
@@ -2620,19 +2368,13 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D99">
-        <v>2</v>
-      </c>
-      <c r="E99">
-        <v>66.7</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -2648,25 +2390,25 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D100">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E100">
-        <v>22.9</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>6-10 ans</t>
+          <t>11-14 ans</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2675,21 +2417,21 @@
         </is>
       </c>
       <c r="D101">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="E101">
-        <v>74.3</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>6-10 ans</t>
+          <t>11-14 ans</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2698,10 +2440,10 @@
         </is>
       </c>
       <c r="D102">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="E102">
-        <v>2.9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="103">
@@ -2717,14 +2459,8 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D103">
-        <v>119</v>
-      </c>
-      <c r="E103">
-        <v>70.40000000000001</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -2735,19 +2471,19 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>11-14 ans</t>
+          <t>15-17 ans</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D104">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E104">
-        <v>29</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="105">
@@ -2758,19 +2494,19 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>11-14 ans</t>
+          <t>15-17 ans</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D105">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E105">
-        <v>0.6</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="106">
@@ -2786,14 +2522,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D106">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E106">
-        <v>49.5</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="107">
@@ -2804,19 +2540,19 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>15-17 ans</t>
+          <t>18-25 ans</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D107">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="E107">
-        <v>41.2</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="108">
@@ -2827,19 +2563,19 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>15-17 ans</t>
+          <t>18-25 ans</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D108">
-        <v>9</v>
+        <v>97</v>
       </c>
       <c r="E108">
-        <v>9.300000000000001</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="109">
@@ -2855,14 +2591,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D109">
-        <v>130</v>
+        <v>54</v>
       </c>
       <c r="E109">
-        <v>46.3</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="110">
@@ -2873,19 +2609,19 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D110">
-        <v>97</v>
+        <v>17</v>
       </c>
       <c r="E110">
-        <v>34.5</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="111">
@@ -2896,19 +2632,13 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D111">
-        <v>49</v>
-      </c>
-      <c r="E111">
-        <v>17.4</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -2919,19 +2649,19 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D112">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E112">
-        <v>1.8</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="113">
@@ -2942,19 +2672,13 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
           <t>Inconnu</t>
         </is>
-      </c>
-      <c r="D113">
-        <v>21</v>
-      </c>
-      <c r="E113">
-        <v>53.8</v>
       </c>
     </row>
     <row r="114">
@@ -2965,7 +2689,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2974,10 +2698,10 @@
         </is>
       </c>
       <c r="D114">
-        <v>17</v>
+        <v>185</v>
       </c>
       <c r="E114">
-        <v>43.6</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="115">
@@ -2988,19 +2712,13 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
           <t>Secondaire 1er cycle</t>
         </is>
-      </c>
-      <c r="D115">
-        <v>1</v>
-      </c>
-      <c r="E115">
-        <v>2.6</v>
       </c>
     </row>
     <row r="116">
@@ -3016,60 +2734,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D116">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E116">
-        <v>12.9</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>6-10 ans</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D117">
-        <v>185</v>
-      </c>
-      <c r="E117">
-        <v>85.3</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>6-10 ans</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D118">
-        <v>4</v>
-      </c>
-      <c r="E118">
-        <v>1.8</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_class_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_class_alaotra_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -401,7 +401,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -418,7 +418,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -435,7 +435,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -452,7 +452,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -498,7 +498,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -515,7 +515,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -532,7 +532,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -549,7 +549,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -618,7 +618,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -641,7 +641,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -664,7 +664,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -681,7 +681,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -704,7 +704,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -750,7 +750,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -767,7 +767,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -784,7 +784,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -807,7 +807,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -824,7 +824,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -870,7 +870,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -910,7 +910,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -944,7 +944,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -984,7 +984,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1007,7 +1007,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1024,7 +1024,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1058,7 +1058,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1098,7 +1098,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1121,7 +1121,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1144,7 +1144,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1167,7 +1167,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1184,7 +1184,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1207,7 +1207,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1230,7 +1230,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1253,7 +1253,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1287,7 +1287,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1310,7 +1310,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1327,7 +1327,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1344,7 +1344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1384,7 +1384,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1407,7 +1407,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1424,7 +1424,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1464,7 +1464,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1504,7 +1504,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1538,7 +1538,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1561,7 +1561,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1578,7 +1578,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1601,7 +1601,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1624,7 +1624,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1647,7 +1647,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1670,7 +1670,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1693,7 +1693,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1710,7 +1710,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1779,7 +1779,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1802,7 +1802,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1819,7 +1819,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1842,7 +1842,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1859,7 +1859,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1882,7 +1882,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1922,7 +1922,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1945,7 +1945,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1962,7 +1962,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1985,7 +1985,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2008,7 +2008,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2031,7 +2031,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2048,7 +2048,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2094,7 +2094,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2111,7 +2111,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2157,7 +2157,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2180,7 +2180,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2203,7 +2203,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2220,7 +2220,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2243,7 +2243,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2266,7 +2266,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2289,7 +2289,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2306,7 +2306,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2323,7 +2323,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2340,7 +2340,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2363,7 +2363,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2380,7 +2380,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2403,7 +2403,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2426,7 +2426,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2449,7 +2449,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2466,7 +2466,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2489,7 +2489,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2512,7 +2512,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2535,7 +2535,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2558,7 +2558,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2581,7 +2581,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2604,7 +2604,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2627,7 +2627,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2644,7 +2644,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2667,7 +2667,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2684,7 +2684,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2707,7 +2707,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2724,7 +2724,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
